--- a/refs/planilhas/Campos_AS_IS_Mapeados.xlsx
+++ b/refs/planilhas/Campos_AS_IS_Mapeados.xlsx
@@ -17,7 +17,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sossego" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="veiculo_abandonado" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'irregular_veiculo'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alvara_ocupacao'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'atividades_economicas'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'desabamento'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'estrutura_imovel'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fiscalizacao_obras'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'meio_ambiente'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'sossego'!$A$1:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'veiculo_abandonado'!$A$1:$F$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -25,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +44,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
-        <bgColor rgb="00D3D3D3"/>
+        <fgColor rgb="002A5788"/>
+        <bgColor rgb="002A5788"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,13 +77,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,12 +474,12 @@
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,490 +515,491 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Logradouro Inexistente</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Número da placa do veículo:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Inserir a(s) placa(s): ABC1234; KVF2779</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Local do estacionamento irregular:</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Selecione o local onde se encontra o veículo</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -972,12 +1013,12 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1013,382 +1054,383 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Atividades exercidas no local:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Indicação da área ocupada:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Tipo de ocupação:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Nome do estabelecimento:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>(razão social (cupom ou nota fiscal) ou nome de fantasia (no letreiro))</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Dias da semana da ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Horário em que ocorre:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1402,12 +1444,12 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1443,578 +1485,579 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Logradouro Inexistente</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Atividades exercidas no local:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Nome do estabelecimento:</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>(razão social (cupom ou nota fiscal) ou nome de fantasia (no letreiro))</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Dias e horários em que a atividade é exercida:</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>É quiosque de praia? :</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>input radio</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Descrição detalhada da ocorrência:</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2028,12 +2071,12 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2069,438 +2112,439 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Comunidade:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>(Selecione a comunidade da ocorrência.)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2514,12 +2558,12 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2555,466 +2599,467 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Logradouro Inexistente</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Comunidade:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>(Selecione a comunidade da ocorrência.)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3028,12 +3073,12 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3069,434 +3114,435 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Logradouro Inexistente</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3510,12 +3556,12 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3551,462 +3597,463 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Logradouro Inexistente</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Telefone para contato:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4020,12 +4067,12 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4061,554 +4108,555 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Telefone para contato:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Quantidade de pessoas:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>(Informe a quantidade de pessoas aglomeradas)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Nome do estabelecimento:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>(razão social (cupom ou nota fiscal) ou nome de fantasia (no letreiro))</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Dias e horários de funcionamento do estabelecimento:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Local de origem do barulho:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>(Selecione de onde vem o barulho)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Fonte do ruído:</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>(Selecione o tipo do ruído)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Local é de difícil acesso:</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Nos casos de obras informe:</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4622,12 +4670,12 @@
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4663,498 +4711,499 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Categoria:</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Tipo/Subtipo:</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Endereço:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Logradouro Inexistente</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>input checkbox</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Número:</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Complemento:</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Localização</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Ponto de Referência:</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Prazo:</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Prazo será exibido ao encaminhar o chamado</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Unidade Organizacional:</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>A UO poderá ser alterada pela Distribuição de Endereço</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>badge/static text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Tipo de solicitante:</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Origem da Ocorrência:</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Descrição da Origem:</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Prioridade:</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>select</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Novo Chamado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Novo Chamado</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Caminho da foto:</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Tempo em que o veículo está abandonado no local:</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>(Informar em anos, ou em meses, ou em dias)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Características do veículo:</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>(Informar modelo, placa, condições aparente)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>input text</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Atributos Específicos</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Descrição:</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Visível</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Visível</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>